--- a/data/trans_orig/IP31KM15_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM15_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19861</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15472</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24381</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>41,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>32866</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>27908</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37104</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>70,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22374</t>
+          <t>30797</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17186</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27587</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>50658</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47220</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62268</t>
+          <t>56950</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17574</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13054</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21963</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>58,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>13629</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9391</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18587</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29,31%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,98%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22911</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17698</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29511</t>
+          <t>23166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44559</t>
+          <t>35391</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>44,17%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>90677</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>80941</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>100981</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>57,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>51,54%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>64,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>101464</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>91384</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>110466</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>63,69%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>57,37%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>69,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>104957</t>
+          <t>92127</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94168</t>
+          <t>82873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117031</t>
+          <t>100701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>206422</t>
+          <t>182804</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>192240</t>
+          <t>169061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>222683</t>
+          <t>196227</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>64,86%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66365</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56061</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76101</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>42,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>48,46%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>57835</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48833</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>67915</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>36,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,63%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>77002</t>
+          <t>53391</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64928</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>87791</t>
+          <t>62645</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>134837</t>
+          <t>119756</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118576</t>
+          <t>106333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149019</t>
+          <t>133499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>112769</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85033</t>
+          <t>100330</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109754</t>
+          <t>125536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>120294</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>107262</t>
+          <t>90801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133750</t>
+          <t>112942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>218024</t>
+          <t>214944</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>199397</t>
+          <t>198503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235077</t>
+          <t>231651</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>61,81%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87357</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>74590</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99796</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>43,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,87%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>75342</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63318</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>88039</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>43,53%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>36,58%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92196</t>
+          <t>72497</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78740</t>
+          <t>61730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>105228</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>167539</t>
+          <t>159854</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>150486</t>
+          <t>143147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186166</t>
+          <t>176295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,04%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>156800</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>139237</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>176090</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>53,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>47,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>60,26%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>129800</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>93856</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>149982</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>47,33%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>54,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>157967</t>
+          <t>135349</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136312</t>
+          <t>121782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>179851</t>
+          <t>150245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>287767</t>
+          <t>292148</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>245169</t>
+          <t>267361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>316994</t>
+          <t>315442</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>57,61%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>135421</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>116131</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>152984</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>46,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>39,74%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>52,35%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>144467</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>124285</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>180411</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>52,67%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>45,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>147032</t>
+          <t>119988</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125148</t>
+          <t>105092</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>168687</t>
+          <t>133555</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>291499</t>
+          <t>255410</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262272</t>
+          <t>232116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>334097</t>
+          <t>280197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>505</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>380108</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>356711</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>407480</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>51,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>59,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>535</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>361860</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>311478</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>388284</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>55,4%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>47,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>59,45%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>505</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>405593</t>
+          <t>360446</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>378260</t>
+          <t>337793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>431631</t>
+          <t>380812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>767453</t>
+          <t>740553</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>715739</t>
+          <t>707394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>806798</t>
+          <t>776670</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,51%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>306716</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>279344</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>330113</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>44,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>40,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>380</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>291274</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>264850</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>341656</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>44,6%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>52,31%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>339140</t>
+          <t>257762</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>313102</t>
+          <t>237396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>366473</t>
+          <t>280415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>630414</t>
+          <t>564478</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>591069</t>
+          <t>528361</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>682128</t>
+          <t>597637</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
